--- a/docs/PRAP_Programming_Specification_v1.41.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.41.xlsx
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>R-62, REQ-DSH-20. SOURCE SCHEMA STEPS 15 TO 16: a thirteenth sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), in LATER_SHEETS, keyed for the import comparison by project_id | month | issue. M.reviews maps 'pid|YYYY-MM|issue' to its row (first row wins). reviewOf(pid, k, dir, gap) returns the review and whether it CLOSES the month: status 'Confirmed - no issue' or 'Accepted' AND gap_fte equal to the current gap in cents. A closed month keeps its gapc / unal marking and gains class rev (muted); gapRows() carries r.rev, and the control, the tile and the list count open issues by direction plus the closed ones apart. S.gapf.rev filters the list (open / closed); #projIssue gains 'reviewed'. A click on [data-gap] is handled BEFORE tr.parent and is a control to the pop-up handler, so it opens openGap(pid, k, dir); drawGap() adds reviewPanel(): #revStatus, #revBy, #revWhy, #revRun over issueRun()'s consecutive months. saveReview() refuses a closing status without a reason and upserts rows through newRow/S.pending; clearReview() deletes over the same reach. reportReviews() (V-40, information) runs after reportUnstaffed in the browser and the Python reference, message for message. No figure moves.</t>
+          <t>R-62, REQ-DSH-20. SOURCE SCHEMA STEPS 15 TO 16: a thirteenth sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), in LATER_SHEETS, keyed for the import comparison by project_id | month | issue. M.reviews maps 'pid|YYYY-MM|issue' to its row (first row wins). reviewOf(pid, k, dir, gap) returns the review and whether it CLOSES the month: status 'Confirmed - no issue' or 'Accepted' AND gap_fte equal to the current gap in cents. A closed month keeps its gapc / unal marking and gains class rev (muted); gapRows() carries r.rev, and the control, the tile and the list count open issues by direction plus the closed ones apart. S.gapf.rev filters the list (open / closed); #projIssue gains 'reviewed'. A click on [data-gap] is handled BEFORE tr.parent and is a control to the pop-up handler, so it opens openGap(pid, k, dir); drawGap() adds reviewPanel(): #revStatus, #revBy, #revWhy, #revRun over issueRun()'s consecutive months. saveReview() refuses a closing status without a reason and upserts rows through newRow/S.pending; clearReview() deletes over the same reach. reportReviews() (V-40, information) runs after reportUnstaffed in the browser and the Python reference, message for message. The Standard vs staffed list is ordered by project ID then month, ascending, and draws every month (GAP_SHOW 40 -&gt; 500, a safety cap). No figure moves.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>OPENED FROM RESOURCE BY PROJECT's own head (R-52), not a section of its own: every month it lists is a cell in that table. THE CONTROL STATES THE FINDING - how many project-months are off their standard and in which direction, with the same arrows and ground the cells use - rather than naming the screen behind it, because the reason for putting this list on the page at all was that a silent fault must not sit behind a click; it is drawn even when there is nothing to report, since a control that comes and goes is one nobody learns the position of. THE LIST CAN BE NARROWED by direction, by project (offering only the projects that have a gap) and by a smallest gap worth looking at; the narrowing reaches the list and nothing else, the heading states n of m whenever anything is set, and a list emptied by its own filter says that rather than that there is nothing to report. Cleared on load. The list itself: every project-month where what the project needs is not what it is getting, largest gap first, with the project, the month, needs, staffed, the gap and its direction. Deliberately NOT a tab - a tab is the surface you visit only once you already suspect a problem, which is the wrong property for something whose whole danger is that it is silent, and the findings report is already the list of everything wrong. Clicking any row opens that month in a dialog: the demand term by term, everyone on it with their applied figures, and EVERY Stated figure editable in place. A month that already has a MonthlyEstimate row is an ordinary contenteditable cell over it, so the editing path of sheet 07 handles it unchanged. A month with NO row has nothing to write through, so its cell CREATES one - and where the assignment is still automatic it asks first, because a lone row against an automatic assignment is read by nothing and setting estimation_type without seeding the other months counts each of them as 0.00 (REQ-CAL-18); the switch, the seeding and the typed figure are then applied together or not at all. Already manual with no row for that month is the V-31 case and is not asked. A cell with no data-sheet is skipped by the generic handler, which is what lets a creating cell carry its own. A row whose Applied is not its Stated carries the V-33 mark. The dialog redraws after an edit; one still showing the gap just closed would read as an edit that did nothing. Empty when there is nothing to report, and it says why rather than disappearing.</t>
+          <t>OPENED FROM RESOURCE BY PROJECT's own head (R-52), not a section of its own: every month it lists is a cell in that table. THE CONTROL STATES THE FINDING - how many project-months are off their standard and in which direction, with the same arrows and ground the cells use - rather than naming the screen behind it, because the reason for putting this list on the page at all was that a silent fault must not sit behind a click; it is drawn even when there is nothing to report, since a control that comes and goes is one nobody learns the position of. THE LIST CAN BE NARROWED by direction, by project (offering only the projects that have a gap) and by a smallest gap worth looking at; the narrowing reaches the list and nothing else, the heading states n of m whenever anything is set, and a list emptied by its own filter says that rather than that there is nothing to report. Cleared on load. The list itself: every project-month where what the project needs is not what it is getting, IN ORDER OF PROJECT ID THEN MONTH, both ascending (numbers inside an ID compare as numbers, so PRJ-2 precedes PRJ-10), with the project, the month, needs, staffed, the gap, its direction and the manager review (R-62). Every month is drawn - GAP_SHOW, 500, is a safety cap a real plan does not reach - because a cap on a list in project order would cut whole projects off the end. Deliberately NOT a tab - a tab is the surface you visit only once you already suspect a problem, which is the wrong property for something whose whole danger is that it is silent, and the findings report is already the list of everything wrong. Clicking any row opens that month in a dialog: the demand term by term, everyone on it with their applied figures, and EVERY Stated figure editable in place. A month that already has a MonthlyEstimate row is an ordinary contenteditable cell over it, so the editing path of sheet 07 handles it unchanged. A month with NO row has nothing to write through, so its cell CREATES one - and where the assignment is still automatic it asks first, because a lone row against an automatic assignment is read by nothing and setting estimation_type without seeding the other months counts each of them as 0.00 (REQ-CAL-18); the switch, the seeding and the typed figure are then applied together or not at all. Already manual with no row for that month is the V-31 case and is not asked. A cell with no data-sheet is skipped by the generic handler, which is what lets a creating cell carry its own. A row whose Applied is not its Stated carries the V-33 mark. The dialog redraws after an edit; one still showing the gap just closed would read as an edit that did nothing. Empty when there is nothing to report, and it says why rather than disappearing.</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
